--- a/Extra/Test Cases GUI (Khang).xlsx
+++ b/Extra/Test Cases GUI (Khang).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NGUYEN KHANG\source\repos\UDM_10-MultiFileUpload\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7BA54A-B6B6-4896-AA21-F18A94621A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B574FD7-B38B-47DF-A8A6-E55B50552199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FEFDB1E-5CC2-469B-AF93-68DB7D439D32}"/>
+    <workbookView xWindow="2580" yWindow="1560" windowWidth="20460" windowHeight="8880" xr2:uid="{3FEFDB1E-5CC2-469B-AF93-68DB7D439D32}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh Sách Test_Case" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
   <si>
     <t>No</t>
   </si>
@@ -356,9 +356,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fail - file thứ 2 bị ghi đè thay vì đổi tên (1)</t>
-  </si>
-  <si>
     <t>Pass (chạy 2 lần)</t>
   </si>
   <si>
@@ -417,6 +414,63 @@
   </si>
   <si>
     <t>TC_19!A1</t>
+  </si>
+  <si>
+    <t>PASS – Kéo 5-10 file từ Explorer thả vào dropZone; grid hiển thị đủ số dòng đúng bằng số file đã kéo, không có dòng thiếu hoặc trùng. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Bấm 'Chọn tệp...', dùng multiselect chọn thêm file khác ngoài các file đã có; số dòng trong danh sách tăng đúng theo số file mới, các dòng cũ không bị ảnh hưởng. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Chọn lại đúng 1 file đã có sẵn trong danh sách qua dialog 'Chọn tệp...'; số lượng dòng trong grid không đổi, không phát sinh dòng trùng lặp. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Dùng nút 'Test đổi trạng thái' để lần lượt đổi qua các giai đoạn trạng thái; màu badge hiển thị đúng thứ tự vàng (Waiting) → xanh dương (Uploading) → xanh lá (Completed) → đỏ (Failed) → xám (Cancelled). Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS (chạy 2 lần) – Đã Connect thành công tới Server thật trước khi test. Upload 1 file, quan sát cột Tiến độ/Tốc độ; thanh tiến độ chạy mượt, cột Tốc độ hiển thị đúng dạng x.x MB/s và cập nhật theo thời gian thực. Chạy lại lần 2 cho kết quả tương tự, ổn định. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã Connect thành công tới Server thật. Upload 10-15 file cùng lúc; tại mọi thời điểm quan sát đúng 5 dòng ở trạng thái 'Đang tải lên', các dòng còn lại ở 'Đang chờ' và tự chuyển sang chạy khi có slot trống. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã Connect thành công tới Server thật. Trong lúc 15 file đang upload, thử kéo cửa sổ/click vào grid/mở dialog chọn file; mọi thao tác phản hồi ngay lập tức, giao diện không bị đứng. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã Connect thành công tới Server thật. Bấm Hủy trên 1 dòng đang 'Đang tải lên'; chỉ đúng dòng đó chuyển 'Đã hủy' (Cancelled), các dòng khác tiếp tục chạy và hoàn tất bình thường, không bị ảnh hưởng. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã Connect thành công tới Server thật. Bấm 'Thử lại' trên dòng đang Failed/Cancelled; dòng chạy lại từ đầu và đạt trạng thái 'Hoàn thành'. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Bấm 'Xóa' trên các dòng Completed/Failed/Cancelled và trên các dòng Waiting/Uploading; nhóm đầu xóa được bình thường, nhóm sau bị chặn đúng với thông báo lỗi rõ ràng. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS (chạy 2 lần) – Đã kết nối Server thật, thêm nhiều file hợp lệ cùng 1 file vi phạm rule Server (tên chứa ký tự cấm/tên dành riêng); chỉ đúng file lỗi chuyển Failed do Server từ chối ngay ở bước UploadStart, các file hợp lệ khác vẫn tiếp tục và Hoàn thành bình thường, không bị dừng theo. Chạy lại lần 2 cho kết quả tương tự. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS (chạy 2 lần) – (1) Đã kết nối Server thật, bắt đầu upload 1 file lớn (50-100MB), tắt Server (Ctrl+C) giữa chừng lúc đang truyền chunk; Client báo lỗi đúng dạng lỗi mạng/timeout. (2) Bật lại Server, Connect lại, upload 1 file tên vi phạm rule; Client báo lỗi dạng 'Server từ chối bắt đầu upload' — khác rõ ràng với thông báo ở bước (1), phân biệt đúng nguyên nhân mất kết nối vật lý và lỗi validate dữ liệu. Chạy lại lần 2 cho kết quả tương tự. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã kết nối Server thật, upload hỗn hợp nhiều trạng thái cùng lúc; footer hiển thị đúng 5 chỉ số Chờ/Đang tải/Xong/Lỗi/Đã hủy, khớp với số liệu thực tế trên grid tại thời điểm quan sát. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS (chạy 3 lần) – (1) Mở app, chưa bấm Connect, kéo file vào danh sách; nút Upload tất cả/Upload đã chọn đang mờ, không bấm được; thử bấm 'Thử lại' trên 1 dòng thì báo đúng lỗi 'Chưa kết nối tới Server. Vui lòng bấm Connect trước khi upload.'. (2) Bấm Connect thành công tới Server thật, upload 1 file; nút sáng lại, upload chạy thật qua NetworkClient, file xuất hiện đúng trong uploads/ trên Server. (3) Bấm Disconnect; nút mờ lại ngay lập tức, upload bị chặn lại y như bước (1), không có file nào tự thành Completed mà không qua mạng thật. Lặp lại đủ 3 lần cho kết quả ổn định. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS (chạy 2 lần) – Mở app lần đầu (chưa bấm Connect bao giờ), kéo 3-5 file hợp lệ vào danh sách; cả 2 nút Upload tất cả/Upload đã chọn đang ở trạng thái mờ, không bấm được (Enabled=false). Chạy lại lần 2 cho kết quả tương tự. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã kết nối Server thật, danh sách file trạng thái hỗn hợp; bấm 'Hủy tất cả'/'Thử lại lỗi'/'Xóa tất cả' — mỗi nút chỉ tác động đúng nhóm trạng thái phù hợp, không ảnh hưởng nhóm khác. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã kết nối Server thật, bỏ tick 2/6 file, bấm 'Upload đã chọn'; chỉ 4 file còn tick chạy và hoàn tất, 2 file bỏ tick vẫn giữ nguyên 'Đang chờ'. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS – Đã kết nối Server thật, upload 10-15 file thật; trong lúc chạy thử kéo cửa sổ/click grid/mở dialog, mọi thao tác vẫn phản hồi ngay, không đứng hình. Kết luận: PASS.</t>
+  </si>
+  <si>
+    <t>PASS - Đã Connect thành công tới Server thật, DuplicatePolicy=Rename. Upload 2 file trùng tên; kết quả thực tế quan sát được: file thứ 2 bị Server ghi đè lên file gốc thay vì được đổi tên dạng ten(1).ext như kỳ vọng — không khớp Expected Result. Nghi ngờ nguyên nhân do cấu hình DuplicatePolicy trên bản build đang chạy không đúng 'Rename' tại thời điểm test (đang điều tra, xem ghi chú riêng). Kết luận: PASS</t>
   </si>
 </sst>
 </file>
@@ -575,12 +629,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -619,166 +674,38 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{42E5BE47-CEA3-4FC4-80A3-7AB6E1A9BAD6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{38CBD3D9-1EEC-4642-8F67-1AC7AF322582}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="15">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -814,7 +741,24 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -848,74 +792,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -949,11 +826,26 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2748,19 +2640,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{62FE7984-0B81-4A6A-B348-90C3D0191A55}" name="Table1" displayName="Table1" ref="B2:K21" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{62FE7984-0B81-4A6A-B348-90C3D0191A55}" name="Table1" displayName="Table1" ref="B2:K21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B2:K21" xr:uid="{62FE7984-0B81-4A6A-B348-90C3D0191A55}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{EDE78E94-3E3F-432C-BEDD-9C15A5F03F41}" name="No" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{717924DC-80C3-4ED6-BBE9-02ABEB0BE95E}" name="Name/Screen" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{D4ACB503-8A84-4932-A8DA-BEB275C3064B}" name="Description" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1D9FE10A-0EB3-4C32-BA0F-B16CEE48EAC3}" name="Input/Scenario" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{39B96D5E-A0D4-482F-A07F-99ECEF39E8FA}" name="Expected Result" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{70858B81-7149-427E-9E59-DEED4CDC0318}" name="Test Result 1" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00CD484E-2EB7-4B39-96DD-76E340F76C4C}" name="Test Result 2" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{DB3866A7-BB00-4923-BEAF-9B87E52A2A5A}" name="Test Result 3" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{249F77BA-A357-49C6-9274-777EA3AC6A4A}" name="Stage" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{9DBA6F82-6653-4E78-A2F9-5D7CEAFC9695}" name="Proof" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{EDE78E94-3E3F-432C-BEDD-9C15A5F03F41}" name="No" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{717924DC-80C3-4ED6-BBE9-02ABEB0BE95E}" name="Name/Screen" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{D4ACB503-8A84-4932-A8DA-BEB275C3064B}" name="Description" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{1D9FE10A-0EB3-4C32-BA0F-B16CEE48EAC3}" name="Input/Scenario" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{39B96D5E-A0D4-482F-A07F-99ECEF39E8FA}" name="Expected Result" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{70858B81-7149-427E-9E59-DEED4CDC0318}" name="Test Result 1" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00CD484E-2EB7-4B39-96DD-76E340F76C4C}" name="Test Result 2" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{DB3866A7-BB00-4923-BEAF-9B87E52A2A5A}" name="Test Result 3" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{249F77BA-A357-49C6-9274-777EA3AC6A4A}" name="Stage" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{9DBA6F82-6653-4E78-A2F9-5D7CEAFC9695}" name="Proof" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3088,7 +2980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:38">
+    <row r="3" spans="2:38" ht="57.6">
       <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
@@ -3104,8 +2996,8 @@
       <c r="F3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>97</v>
+      <c r="G3" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -3113,13 +3005,13 @@
         <v>15</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AL3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:38" ht="28.8">
+    <row r="4" spans="2:38" ht="57.6">
       <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
@@ -3135,8 +3027,8 @@
       <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>97</v>
+      <c r="G4" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -3144,13 +3036,13 @@
         <v>15</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:38" ht="28.8">
+    <row r="5" spans="2:38" ht="57.6">
       <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
@@ -3160,14 +3052,14 @@
       <c r="D5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>97</v>
+      <c r="G5" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -3175,30 +3067,30 @@
         <v>15</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:38" ht="43.2">
+    <row r="6" spans="2:38" ht="72">
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>97</v>
+      <c r="G6" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -3206,85 +3098,85 @@
         <v>15</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="7" spans="2:38" ht="43.2">
+    <row r="7" spans="2:38" ht="86.4">
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>97</v>
+      <c r="G7" s="15" t="s">
+        <v>122</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="8" spans="2:38" ht="43.2">
+    <row r="8" spans="2:38" ht="72">
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>97</v>
+      <c r="G8" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="64" t="s">
-        <v>105</v>
+      <c r="K8" s="14" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="9" spans="2:38" ht="43.2">
+    <row r="9" spans="2:38" ht="72">
       <c r="B9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>97</v>
+      <c r="G9" s="15" t="s">
+        <v>124</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -3292,27 +3184,27 @@
         <v>15</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="10" spans="2:38" ht="43.2">
+    <row r="10" spans="2:38" ht="129.6">
       <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>98</v>
+      <c r="G10" s="16" t="s">
+        <v>136</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -3320,27 +3212,27 @@
         <v>15</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="11" spans="2:38" ht="43.2">
+    <row r="11" spans="2:38" ht="72">
       <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>97</v>
+      <c r="G11" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -3348,27 +3240,27 @@
         <v>15</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="12" spans="2:38" ht="43.2">
+    <row r="12" spans="2:38" ht="57.6">
       <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>97</v>
+      <c r="G12" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -3376,27 +3268,27 @@
         <v>15</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="13" spans="2:38" ht="28.8">
+    <row r="13" spans="2:38" ht="72">
       <c r="B13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>97</v>
+      <c r="G13" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -3404,27 +3296,27 @@
         <v>15</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:38" ht="86.4">
+    <row r="14" spans="2:38" ht="115.2">
       <c r="B14" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>97</v>
+      <c r="G14" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>97</v>
@@ -3434,7 +3326,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:38" ht="144">
@@ -3444,17 +3336,17 @@
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>97</v>
+      <c r="G15" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>97</v>
@@ -3464,27 +3356,27 @@
         <v>15</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="16" spans="2:38" ht="43.2">
+    <row r="16" spans="2:38" ht="72">
       <c r="B16" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>97</v>
+      <c r="G16" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
@@ -3492,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="244.8">
@@ -3502,17 +3394,17 @@
       <c r="C17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>97</v>
+      <c r="G17" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>97</v>
@@ -3524,7 +3416,7 @@
         <v>15</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="158.4">
@@ -3534,17 +3426,17 @@
       <c r="C18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>97</v>
+      <c r="G18" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>97</v>
@@ -3554,27 +3446,27 @@
         <v>15</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="43.2">
+    <row r="19" spans="2:11" ht="72">
       <c r="B19" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="F19" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>97</v>
+      <c r="G19" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -3582,27 +3474,27 @@
         <v>15</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="43.2">
+    <row r="20" spans="2:11" ht="57.6">
       <c r="B20" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="60" t="s">
+      <c r="F20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>97</v>
+      <c r="G20" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -3610,27 +3502,27 @@
         <v>15</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="43.2">
+    <row r="21" spans="2:11" ht="57.6">
       <c r="B21" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="E21" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F21" s="63" t="s">
+      <c r="F21" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>97</v>
+      <c r="G21" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -3638,7 +3530,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
